--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486479_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486479_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0097</v>
+        <v>3.5879</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6584</v>
+        <v>4.2366</v>
       </c>
       <c r="F2" t="n">
         <v>-0.6487000000000001</v>
@@ -610,10 +610,10 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6081</v>
+        <v>0.1863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5997</v>
+        <v>0.1779</v>
       </c>
       <c r="U2" t="n">
         <v>0.008399999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9242</v>
+        <v>2.4665</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1442</v>
+        <v>2.8285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
+        <v>-0.362</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4887</v>
+        <v>1.646</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2161</v>
+        <v>-2.6825</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2726</v>
+        <v>4.3285</v>
       </c>
       <c r="J3" t="n">
-        <v>1.476</v>
+        <v>3.3627</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8641</v>
+        <v>-0.1762</v>
       </c>
       <c r="L3" t="n">
-        <v>0.612</v>
+        <v>3.5389</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0127</v>
+        <v>-1.7167</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6479</v>
+        <v>-2.5063</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6606</v>
+        <v>0.7897</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5432</v>
+        <v>-0.1148</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7557</v>
+        <v>-0.5119</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2125</v>
+        <v>0.3972</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7602</v>
+        <v>-0.3698</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9442</v>
+        <v>2.0053</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2445</v>
+        <v>1.1636</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3003</v>
+        <v>0.8417</v>
       </c>
       <c r="G4" t="n">
-        <v>1.646</v>
+        <v>1.4887</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6825</v>
+        <v>0.2161</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3285</v>
+        <v>1.2726</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3627</v>
+        <v>1.476</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1762</v>
+        <v>0.8641</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5389</v>
+        <v>0.612</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7167</v>
+        <v>0.0127</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5063</v>
+        <v>-0.6479</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7897</v>
+        <v>0.6606</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6371</v>
+        <v>0.6243</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0959</v>
+        <v>0.7751</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4588</v>
+        <v>-0.1508</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8427</v>
+        <v>1.4516</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4384</v>
+        <v>0.2322</v>
       </c>
       <c r="F5" t="n">
-        <v>1.281</v>
+        <v>1.2194</v>
       </c>
       <c r="G5" t="n">
         <v>-3.0939</v>
@@ -844,13 +844,13 @@
         <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9111</v>
+        <v>-0.3022</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4675</v>
+        <v>0.2031</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4437</v>
+        <v>-0.5053</v>
       </c>
       <c r="V5" t="n">
         <v>2.4552</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1254</v>
+        <v>0.0866</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1187</v>
+        <v>-1.2594</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0066</v>
+        <v>1.346</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2627</v>
+        <v>-0.277</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7877</v>
+        <v>-1.183</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4749</v>
+        <v>0.906</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0298</v>
+        <v>0.0108</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1063</v>
+        <v>-0.4681</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>0.4789</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2328</v>
+        <v>-0.2878</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6814</v>
+        <v>-0.7149</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5514</v>
+        <v>0.4271</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3853</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1286</v>
+        <v>-0.1826</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5138</v>
+        <v>-0.3461</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3285</v>
+        <v>-0.0333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4246</v>
+        <v>-1.8717</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7531</v>
+        <v>1.8384</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7658</v>
+        <v>-2.0701</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3953</v>
+        <v>-0.7633</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3705</v>
+        <v>-1.3068</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08690000000000001</v>
+        <v>-1.8158</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3531</v>
+        <v>-0.2309</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2661</v>
+        <v>-1.5849</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8528</v>
+        <v>-0.2543</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7484</v>
+        <v>-0.5324</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1044</v>
+        <v>0.2781</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>0.675</v>
+        <v>-0.551</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4252</v>
+        <v>-0.2511</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7502</v>
+        <v>-0.2998</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3489</v>
+        <v>-0.1139</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8182</v>
+        <v>-0.2305</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4693</v>
+        <v>0.1167</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.277</v>
+        <v>-1.2627</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.183</v>
+        <v>-0.7877</v>
       </c>
       <c r="I8" t="n">
-        <v>0.906</v>
+        <v>-0.4749</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0108</v>
+        <v>-0.0298</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4681</v>
+        <v>-0.1063</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4789</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2878</v>
+        <v>-1.2328</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7149</v>
+        <v>-0.6814</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4271</v>
+        <v>-0.5514</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.3737</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2228</v>
+        <v>-0.3906</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-1.0068</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4305</v>
+        <v>-0.4694</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7768</v>
+        <v>-0.5374</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0701</v>
+        <v>-0.7658</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7633</v>
+        <v>-0.3953</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3068</v>
+        <v>-0.3705</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8158</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2309</v>
+        <v>0.3531</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5849</v>
+        <v>-0.2661</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2543</v>
+        <v>-0.8528</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5324</v>
+        <v>-0.7484</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>-0.1044</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.1751</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.5345</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.3252</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.3926</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.1714</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.8099</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.3615</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1952</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>A. VRABAC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0729</v>
+        <v>-1.3714</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3291</v>
+        <v>-0.1629</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7437</v>
+        <v>-1.2086</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6103</v>
+        <v>-0.6183</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4288</v>
+        <v>-2.2048</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0391</v>
+        <v>1.5865</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5101</v>
+        <v>1.3629</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2806</v>
+        <v>0.119</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2295</v>
+        <v>1.2439</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8998</v>
+        <v>-1.9812</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7094</v>
+        <v>-2.3238</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8096</v>
+        <v>0.3426</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7741</v>
+        <v>-0.1229</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1406</v>
+        <v>-0.2632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6335</v>
+        <v>0.1403</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9347</v>
+        <v>-0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VRABAC</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.098</v>
+        <v>-1.7665</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8586</v>
+        <v>-0.7762</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2394</v>
+        <v>-0.9903</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6183</v>
+        <v>0.6103</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2048</v>
+        <v>-0.4288</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5865</v>
+        <v>1.0391</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3629</v>
+        <v>1.5101</v>
       </c>
       <c r="K11" t="n">
-        <v>0.119</v>
+        <v>1.2806</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2439</v>
+        <v>0.2295</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9812</v>
+        <v>-0.8998</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3238</v>
+        <v>-1.7094</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3426</v>
+        <v>0.8096</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8495</v>
+        <v>0.0805</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>-0.3064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1095</v>
+        <v>0.3869</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1952</v>
+        <v>-0.9347</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9083</v>
+        <v>-2.436</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8945</v>
+        <v>-2.4223</v>
       </c>
       <c r="F12" t="n">
         <v>-0.0137</v>
@@ -1390,10 +1390,10 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.019</v>
+        <v>-0.5468</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0274</v>
+        <v>-0.5552</v>
       </c>
       <c r="U12" t="n">
         <v>0.008399999999999999</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.185100000000001</v>
+        <v>2.87</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5836999999999986</v>
+        <v>1.268500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6016</v>
+        <v>1.6015</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.960400000000001</v>
+        <v>-1.9604</v>
       </c>
       <c r="H13" t="n">
         <v>-14.8256</v>
@@ -1441,10 +1441,10 @@
         <v>12.8653</v>
       </c>
       <c r="J13" t="n">
-        <v>9.384500000000001</v>
+        <v>9.384499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3680999999999999</v>
+        <v>0.3681000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>9.0167</v>
@@ -1459,7 +1459,7 @@
         <v>3.8487</v>
       </c>
       <c r="P13" t="n">
-        <v>7.612699999999998</v>
+        <v>7.6127</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.0503</v>
@@ -1468,10 +1468,10 @@
         <v>20.6634</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3372</v>
+        <v>-1.6523</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0512</v>
+        <v>-0.3663000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2859</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8099</v>
+        <v>4.5441</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6979</v>
+        <v>2.5862</v>
       </c>
       <c r="F14" t="n">
-        <v>2.112</v>
+        <v>1.9579</v>
       </c>
       <c r="G14" t="n">
         <v>3.7796</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0977</v>
+        <v>0.8319</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2896</v>
+        <v>0.1779</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8081</v>
+        <v>0.654</v>
       </c>
       <c r="V14" t="n">
         <v>1.8902</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9524</v>
+        <v>2.1162</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4103</v>
+        <v>-0.1485</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5421</v>
+        <v>2.2647</v>
       </c>
       <c r="G15" t="n">
         <v>1.8259</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1716</v>
+        <v>1.3354</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1032</v>
+        <v>0.5444</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0684</v>
+        <v>0.791</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8072</v>
+        <v>1.8303</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2013</v>
+        <v>-0.0222</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6059</v>
+        <v>1.8525</v>
       </c>
       <c r="G16" t="n">
         <v>0.8978</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1781</v>
+        <v>-0.155</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2211</v>
+        <v>-0.0024</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3992</v>
+        <v>-0.1526</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8206</v>
+        <v>1.3473</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9892</v>
+        <v>2.2127</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1686</v>
+        <v>-0.8655</v>
       </c>
       <c r="G17" t="n">
         <v>1.4047</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7793</v>
+        <v>-0.2527</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1815</v>
+        <v>0.0421</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5979</v>
+        <v>-0.2947</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0521</v>
+        <v>0.5865</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2021</v>
+        <v>0.2449</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2542</v>
+        <v>0.3415</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0642</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1012</v>
+        <v>0.4332</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5239</v>
+        <v>-0.0769</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4227</v>
+        <v>0.5101</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4407</v>
+        <v>-0.0323</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9892</v>
+        <v>-1.7657</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5485</v>
+        <v>1.7334</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1481</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1627</v>
+        <v>0.2457</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1815</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0187</v>
+        <v>0.2037</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0925</v>
+        <v>-1.51</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8097</v>
+        <v>1.0273</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9021</v>
+        <v>-2.5374</v>
       </c>
       <c r="G20" t="n">
         <v>0.9228</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2674</v>
+        <v>0.8499</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3772</v>
+        <v>0.5948</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1097</v>
+        <v>0.2551</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3252</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2903</v>
+        <v>-2.1159</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0838</v>
+        <v>-1.1286</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2065</v>
+        <v>-0.9873</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8707</v>
+        <v>-2.7746</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0427</v>
+        <v>0.2798</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.828</v>
+        <v>-3.0543</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6538</v>
+        <v>-1.3863</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0912</v>
+        <v>-0.4134</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7451</v>
+        <v>-0.9729</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2169</v>
+        <v>-1.3882</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1339</v>
+        <v>0.6932</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0829</v>
+        <v>-2.0814</v>
       </c>
       <c r="P21" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2021</v>
+        <v>0.3112</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3425</v>
+        <v>-0.1322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1404</v>
+        <v>0.4434</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5744</v>
+        <v>-2.1284</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4639</v>
+        <v>-1.8603</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1106</v>
+        <v>-0.2681</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7746</v>
+        <v>-1.8707</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2798</v>
+        <v>-0.0427</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0543</v>
+        <v>-1.828</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3863</v>
+        <v>-0.6538</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4134</v>
+        <v>0.0912</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9729</v>
+        <v>-0.7451</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3882</v>
+        <v>-1.2169</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6932</v>
+        <v>-0.1339</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0814</v>
+        <v>-1.0829</v>
       </c>
       <c r="P22" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1473</v>
+        <v>-0.0403</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>-0.119</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3201</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7708</v>
+        <v>-2.7374</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7795</v>
+        <v>-0.556</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9913</v>
+        <v>-2.1814</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1867</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1491</v>
+        <v>-0.1157</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1009</v>
+        <v>0.1226</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0482</v>
+        <v>-0.2382</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4585</v>
+        <v>-3.3403</v>
       </c>
       <c r="E24" t="n">
         <v>-2.1913</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2672</v>
+        <v>-1.149</v>
       </c>
       <c r="G24" t="n">
         <v>1.1739</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4796</v>
+        <v>-0.3614</v>
       </c>
       <c r="T24" t="n">
         <v>0.0925</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.4539</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3252</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.184999999999999</v>
+        <v>-1.439899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.601399999999999</v>
+        <v>-1.6015</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5836000000000001</v>
+        <v>0.1613000000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>1.960400000000001</v>
+        <v>1.9604</v>
       </c>
       <c r="H25" t="n">
         <v>14.8257</v>
@@ -2386,7 +2386,7 @@
         <v>-3.848800000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.384600000000001</v>
+        <v>-9.384599999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-0.3679999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.0503</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3373</v>
+        <v>3.082199999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2858</v>
+        <v>1.2859</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0513</v>
+        <v>1.7966</v>
       </c>
       <c r="V25" t="n">
         <v>1.13</v>
